--- a/docs/Logic Requirements/Ageipelago Vlad Dracula.xlsx
+++ b/docs/Logic Requirements/Ageipelago Vlad Dracula.xlsx
@@ -5,15 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb6dd295c338e39f/Desktop/Logic Requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="8_{FE8C729A-FBED-4542-8B98-A1835FA1F684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A265E1A0-FCF7-498A-A61D-9EA7F38A2EE4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B5734D-8B42-40BB-8796-A25DC3140BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Vlad Dracula" sheetId="1" r:id="rId1"/>
+    <sheet name="The Dragon Spreads his Wings" sheetId="2" r:id="rId2"/>
+    <sheet name="The Return of the Dragon" sheetId="3" r:id="rId3"/>
+    <sheet name="The Breath of the Dragon" sheetId="4" r:id="rId4"/>
+    <sheet name="The Moon Rises" sheetId="5" r:id="rId5"/>
+    <sheet name="The Night Falls" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="230">
   <si>
     <t>Scenario</t>
   </si>
@@ -232,108 +237,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Moderate:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Starting Units:
-13 Two-Handed Swordsmen
-33 Pikemen
-11 Crossbowmen
-7 Elite Skirmishers
-9 Hand Cannoneers
-6 Light Cavalry
-9 Boyars
-2 Scorpions
-1 Capped Ram
-Later:
-6 Two-Handed Swordsmen
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Standard:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Starting Units:
-13 Long Swordsmen
-33 Pikemen
-11 Crossbowmen
-7 Elite Skirmishers
-9 Hand Cannoneers
-6 Light Cavalry
-9 Boyars
-Later:
-4 Long Swordsmen
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Hard:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Starting Units:
-13 Champions
-33 Pikemen
-11 Crossbowmen
-7 Elite Skirmishers
-9 Hand Cannoneers
-6 Light Cavalry
-9 Boyars
-4 Scorpions
-1 Mangonel
-1 Capped Ram
-Later:
-8 Champions</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Meet </t>
     </r>
     <r>
@@ -1913,178 +1816,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-10 Paladins
-12 Elite Magyar Huszars
-10 Heavy Cavalry Archers
-2 Trebuchets
-4 Galleons
-4 Fast Fire Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-4 Paladins
-5 Elite Magyar Huszars
-5 Heavy Cavalry Archers
-1 Trebuchet
-4 Galleons
-4 Fast Fire Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Identical to Moderate</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-3 Pikemen
-3 Crossbowmen
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-10 Boyars
-20 Crossbowmen
-3 Mangonels
-4 Battering Rams
-5 Monks
-4 War Galleys
-4 Fire Ships
-4 Demolition Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-3 Boyars
-8 Crossbowmen
-4 Battering Rams
-2 Monks
-4 War Galleys
-4 Fire Ships
-4 Demolition Ships
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-Identical to Moderate</t>
     </r>
   </si>
   <si>
@@ -2617,95 +2348,6 @@
   <si>
     <r>
       <t xml:space="preserve">Starting Units:
-8 Pikemen
-7 Boyars
-1 Capped Ram
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-10 Pikemen
-2 Hussars
-10 Elite Boyars
-2 Capped Rams
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-5 Pikemen
-2 Hussars
-5 Boyars
-1 Batterin Ram
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-15 Pikemen
-2 Hussars
-15 Elite Boyars
-3 Siege Rams</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
 7 Long Swordsmen
 7 Janissaries
 1 Bombard Cannon
@@ -3035,14 +2677,6 @@
     <t>Player 7 cannot be defeated, as they do not start with any Units and simply keep spawning in Cavalry to harass Player 2.
 This Mission is meant to be played VERY defensively, only requiering the Player to survive for 1 Hour. This also makes it annoying, as it will always take, well, 1 Hour. Defeating the Enemies here will be quite difficult. I would recommend making the Central Base with the Monks and Monestaries and the starting Units and/or Resources an item, as there is not much else to unlock, as the outer Bases all need to be defended.
 Maybe add a progressive Goal for the Number of Castles still standing at the end of the Mission?</t>
-  </si>
-  <si>
-    <t>Starting Units:
-1 Champien
-1 Condottiero
-3 Heavy Pikemen
-4 Elite Genoese Crossbowman
-1 Chavalier</t>
   </si>
   <si>
     <t>11 Champions
@@ -3477,77 +3111,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Watchtower</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> x3
-Destroy </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Tower of Flies</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Tribute 1000 Food to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Wallachia</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Reach </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Poenari Castle</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="14"/>
@@ -3908,6 +3471,1273 @@
 7 Elite Skirmishers
 3 Battering Rams
 10 Galleys</t>
+    </r>
+  </si>
+  <si>
+    <t>Killable Units</t>
+  </si>
+  <si>
+    <t>Destructible Buildings</t>
+  </si>
+  <si>
+    <t>Deer</t>
+  </si>
+  <si>
+    <t>No items required</t>
+  </si>
+  <si>
+    <t>Guard Tower</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <t>Archery Range</t>
+  </si>
+  <si>
+    <t>Pikeman</t>
+  </si>
+  <si>
+    <t>Siege Workshop</t>
+  </si>
+  <si>
+    <t>Crossbowman</t>
+  </si>
+  <si>
+    <t>Elite Skirmisher</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>Knight</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>Light Cavalry</t>
+  </si>
+  <si>
+    <t>Mill</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Dock</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Lumber Camp</t>
+  </si>
+  <si>
+    <t>Mining Camp</t>
+  </si>
+  <si>
+    <t>Capped Ram</t>
+  </si>
+  <si>
+    <t>Fortified Wall</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Palisade Wall</t>
+  </si>
+  <si>
+    <t>Long Swordsman</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>Monastery</t>
+  </si>
+  <si>
+    <t>Town Center</t>
+  </si>
+  <si>
+    <t>Two-Handed Swordsman</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>Trebuchet</t>
+  </si>
+  <si>
+    <t>Trade Workshop</t>
+  </si>
+  <si>
+    <t>Pavilion</t>
+  </si>
+  <si>
+    <t>Pavilion (Large)</t>
+  </si>
+  <si>
+    <t>Ibex</t>
+  </si>
+  <si>
+    <t>Grey Wolf</t>
+  </si>
+  <si>
+    <t>Hand Cannoneer</t>
+  </si>
+  <si>
+    <t>Boyar</t>
+  </si>
+  <si>
+    <t>Man-at-Arms</t>
+  </si>
+  <si>
+    <t>Spearman</t>
+  </si>
+  <si>
+    <t>Galley</t>
+  </si>
+  <si>
+    <t>War Galley</t>
+  </si>
+  <si>
+    <t>Voivod Istvan</t>
+  </si>
+  <si>
+    <t>Voivod Mircea</t>
+  </si>
+  <si>
+    <t>Voivod Jakub</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Moderate:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Starting Units:
+13 Long Swordsmen
+33 Pikemen
+11 Crossbowmen
+7 Elite Skirmishers
+9 Hand Cannoneers
+6 Light Cavalry
+9 Boyars
+2 Scorpions
+1 Capped Ram
+Later:
+6 Two-Handed Swordsmen
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Standard:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Starting Units:
+13 Long Swordsmen
+33 Pikemen
+11 Crossbowmen
+7 Elite Skirmishers
+9 Hand Cannoneers
+6 Light Cavalry
+9 Boyars
+Later:
+4 Long Swordsmen
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Hard:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Starting Units:
+13 Long Swordsmen
+33 Pikemen
+11 Crossbowmen
+7 Elite Skirmishers
+9 Hand Cannoneers
+6 Light Cavalry
+9 Boyars
+4 Scorpions
+1 Mangonel
+1 Capped Ram
+Later:
+8 Champions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Two-Handed Swordsmen
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Moderate)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Champion
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mangonel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Scorpion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Stone Gate</t>
+  </si>
+  <si>
+    <t>Stone Wall</t>
+  </si>
+  <si>
+    <t>Bombard Tower</t>
+  </si>
+  <si>
+    <t>Fire Tower</t>
+  </si>
+  <si>
+    <t>Gunpowder Tower</t>
+  </si>
+  <si>
+    <t>Watch Tower</t>
+  </si>
+  <si>
+    <t>Blacksmith</t>
+  </si>
+  <si>
+    <t>Converts to Player</t>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>Cavalry Archer</t>
+  </si>
+  <si>
+    <t>Heavy Cavalry Archer</t>
+  </si>
+  <si>
+    <t>Heavy Pikeman</t>
+  </si>
+  <si>
+    <t>Danesti General</t>
+  </si>
+  <si>
+    <t>Monk</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Battering Ram
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Boyar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elite Boyar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Capped Ram
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Moderate)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Heavy Scorpion
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Siege Ram
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Bogdan II, Voivod of Moldavia</t>
+  </si>
+  <si>
+    <t>Despawns in Vanilla</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Siege Ram
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Capped Ram
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Halberdier
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Hussar</t>
+  </si>
+  <si>
+    <t>Elite Magyar Huszar</t>
+  </si>
+  <si>
+    <t>Magyar Huszar</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Paladin
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Jannissary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Only on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Elite Jannissary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bombard Cannon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Outpost</t>
+  </si>
+  <si>
+    <t>Barricade</t>
+  </si>
+  <si>
+    <t>Fortified Gare</t>
+  </si>
+  <si>
+    <t>Vladislav II</t>
+  </si>
+  <si>
+    <t>Fortified Palisade Wall</t>
+  </si>
+  <si>
+    <t>Bran Castle</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+10 Knights
+12 Magyar Huszars
+10 Cavalry Archers
+4 War Galleys
+4 Fire Ships
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+4 Knights
+5 Magyar Huszars
+5 Cavalry Archers
+4 War Galleys
+4 Fire Ships
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+10 Paladins
+12 Elite Magyar Huszars
+10 Heavy Cavalry Archers
+2 Trebuchets
+4 Galleons
+4 Fast Fire Ships</t>
+    </r>
+  </si>
+  <si>
+    <t>Wild Boar</t>
+  </si>
+  <si>
+    <t>Pig</t>
+  </si>
+  <si>
+    <t>Janissary</t>
+  </si>
+  <si>
+    <t>Bombard Cannon</t>
+  </si>
+  <si>
+    <t>Elite Janissary</t>
+  </si>
+  <si>
+    <t>Cannon Galleon</t>
+  </si>
+  <si>
+    <t>Galleon</t>
+  </si>
+  <si>
+    <t>Heavy Camel Rider</t>
+  </si>
+  <si>
+    <t>Camel Rider</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elite Cannon Galleon
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Fire Ship</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fast Fire Ship
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cavalier
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Paladin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Heavy Cavalry Archer
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elite Magyar Huszar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Battering Ram</t>
+  </si>
+  <si>
+    <t>Fishing Ship</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trebuchet
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Trade Cog</t>
+  </si>
+  <si>
+    <t>War Hulk</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+3 Pikemen
+3 Crossbowmen
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+10 Boyars
+20 Crossbowmen
+3 Mangonels
+4 Battering Rams
+5 Monks
+4 War Galleys
+4 Fire Ships
+2 War Hulk
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+3 Boyars
+8 Crossbowmen
+4 Battering Rams
+2 Monks
+4 War Galleys
+4 Fire Ships
+2 War Hulk
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+Identical to Moderate</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mangonel
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Skirmisher</t>
+  </si>
+  <si>
+    <t>Scout Cavalry</t>
+  </si>
+  <si>
+    <t>Requires Dock</t>
+  </si>
+  <si>
+    <t>Sea Wall</t>
+  </si>
+  <si>
+    <t>Sea Gate</t>
+  </si>
+  <si>
+    <t>Palisade Gate</t>
+  </si>
+  <si>
+    <t>Fortified Gate</t>
+  </si>
+  <si>
+    <t>Fish Trap</t>
+  </si>
+  <si>
+    <t>Trade Cart</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+8 Pikemen
+7 Boyars
+1 Capped Ram
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+10 Pikemen
+2 Hussars
+10 Elite Boyars
+2 Capped Rams
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+5 Pikemen
+2 Hussars
+5 Boyars
+1 Battering Ram
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+15 Pikemen
+2 Hussars
+15 Elite Boyars
+3 Siege Rams</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Elite Janissary
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Petard</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cavalier</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trebuchet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Only on Hard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Paladin</t>
+  </si>
+  <si>
+    <t>Transport Ship</t>
+  </si>
+  <si>
+    <t>Horse</t>
+  </si>
+  <si>
+    <t>Fence</t>
+  </si>
+  <si>
+    <t>Likely unreachable</t>
+  </si>
+  <si>
+    <t>Knights</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Scorpion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Halberdier</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trebuchet
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF2FE2F5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Skirmisher</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Only on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Starting Units:
+1 Champien
+1 Condottiero
+3 Heavy Pikemen
+4 Elite Genoese Crossbowman
+1 Cavalier</t>
+  </si>
+  <si>
+    <t>Craftsman</t>
+  </si>
+  <si>
+    <t>Condottiero</t>
+  </si>
+  <si>
+    <t>Elite Genoese Crossbowman</t>
+  </si>
+  <si>
+    <t>Fortified Tower</t>
+  </si>
+  <si>
+    <t>Old Tower</t>
+  </si>
+  <si>
+    <t>Abandoned Tower</t>
+  </si>
+  <si>
+    <t>City Wall</t>
+  </si>
+  <si>
+    <t>Poenari Castle</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Watchtower</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> x3
+Destroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fortifed Tower</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Tribute 1000 Food to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Wallachia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Reach </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Poenari Castle</t>
     </r>
   </si>
 </sst>
@@ -4064,7 +4894,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -4152,11 +4982,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4192,6 +5044,60 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4589,26 +5495,26 @@
         <v>16</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>21</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>23</v>
@@ -4623,7 +5529,7 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4631,49 +5537,49 @@
         <v>17</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="H5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="N5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="O5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="N5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="Q5" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4681,47 +5587,47 @@
         <v>18</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>53</v>
-      </c>
       <c r="J6" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="P6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="N6" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="P6" s="7" t="s">
-        <v>59</v>
-      </c>
       <c r="Q6" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4729,43 +5635,43 @@
         <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>65</v>
+        <v>205</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="O7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q7" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="P7" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4773,44 +5679,44 @@
         <v>20</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>81</v>
+        <v>229</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F8" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>79</v>
-      </c>
       <c r="I8" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>73</v>
+        <v>220</v>
       </c>
       <c r="Q8" s="7"/>
     </row>
@@ -4836,4 +5742,2845 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F02C8E1-0617-48AE-97CC-71F03F7EACB1}">
+  <dimension ref="G1:L52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G14" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G15" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G16" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="G17" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+    </row>
+    <row r="43" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+    </row>
+    <row r="44" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+    </row>
+    <row r="45" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+    </row>
+    <row r="46" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
+    </row>
+    <row r="47" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+    </row>
+    <row r="48" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+    </row>
+    <row r="49" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="K49" s="20"/>
+      <c r="L49" s="20"/>
+    </row>
+    <row r="50" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="K50" s="20"/>
+      <c r="L50" s="20"/>
+    </row>
+    <row r="51" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+    </row>
+    <row r="52" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66D5B1F3-605B-4EBE-ADC3-86093F9414AB}">
+  <dimension ref="G1:L52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G6" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G8" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G16" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G22" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G23" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K25" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K27" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G28" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K28" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G29" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K29" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K30" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G31" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K31" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G32" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="K32" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K33" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="L33" s="19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G34" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+    </row>
+    <row r="36" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G36" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+    </row>
+    <row r="37" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G37" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+    </row>
+    <row r="38" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G38" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20"/>
+    </row>
+    <row r="39" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G39" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+    </row>
+    <row r="43" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+    </row>
+    <row r="44" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+    </row>
+    <row r="45" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+    </row>
+    <row r="46" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
+    </row>
+    <row r="47" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+    </row>
+    <row r="48" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+    </row>
+    <row r="49" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="K49" s="20"/>
+      <c r="L49" s="20"/>
+    </row>
+    <row r="50" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="K50" s="20"/>
+      <c r="L50" s="20"/>
+    </row>
+    <row r="51" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+    </row>
+    <row r="52" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E160A0EB-2282-4E17-8E90-A75C2FBB2FDB}">
+  <dimension ref="G1:L52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G11" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G22" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G23" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G24" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G25" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G26" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G33" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K34" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G35" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+    </row>
+    <row r="43" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G43" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+    </row>
+    <row r="44" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+    </row>
+    <row r="45" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+    </row>
+    <row r="46" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
+    </row>
+    <row r="47" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+    </row>
+    <row r="48" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+    </row>
+    <row r="49" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="K49" s="20"/>
+      <c r="L49" s="20"/>
+    </row>
+    <row r="50" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="K50" s="20"/>
+      <c r="L50" s="20"/>
+    </row>
+    <row r="51" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+    </row>
+    <row r="52" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D5F9A79-9995-4745-9487-825DE3743A9E}">
+  <dimension ref="G1:L52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G12" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G13" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G14" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G23" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K23" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G26" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+    </row>
+    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G27" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+    </row>
+    <row r="43" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+    </row>
+    <row r="44" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+    </row>
+    <row r="45" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+    </row>
+    <row r="46" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
+    </row>
+    <row r="47" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+    </row>
+    <row r="48" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+    </row>
+    <row r="49" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="K49" s="20"/>
+      <c r="L49" s="20"/>
+    </row>
+    <row r="50" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="K50" s="20"/>
+      <c r="L50" s="20"/>
+    </row>
+    <row r="51" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+    </row>
+    <row r="52" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B39F4FDB-FAC5-4FF4-809E-E36473FC3DC6}">
+  <dimension ref="G1:L52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G12" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G22" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G23" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K23" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G29" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K29" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G31" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K34" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="L34" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G35" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+    </row>
+    <row r="43" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+    </row>
+    <row r="44" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+    </row>
+    <row r="45" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+    </row>
+    <row r="46" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
+    </row>
+    <row r="47" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+    </row>
+    <row r="48" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+    </row>
+    <row r="49" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="K49" s="20"/>
+      <c r="L49" s="20"/>
+    </row>
+    <row r="50" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="K50" s="20"/>
+      <c r="L50" s="20"/>
+    </row>
+    <row r="51" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+    </row>
+    <row r="52" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>